--- a/_Requirement_Procurement.xlsx
+++ b/_Requirement_Procurement.xlsx
@@ -1,24 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thainamthip2-my.sharepoint.com/personal/sutripat_ng_thainamthip_co_th/Documents/1. Work/008. Procurement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C66B6C0B-CF9C-45D2-96C4-3473E576E881}"/>
+  <xr:revisionPtr revIDLastSave="706" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C6D0A52-6B34-4B12-BC57-E5CCCA9B10AC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EB3B1C72-C041-46E4-89A3-B2646AB90CFA}"/>
   </bookViews>
   <sheets>
-    <sheet name="1_ปรับปรุงสูตร vs PY ที่ตัวเก่า" sheetId="1" r:id="rId1"/>
-    <sheet name="2_PJ202510" sheetId="2" r:id="rId2"/>
-    <sheet name="3_CR2059" sheetId="3" r:id="rId3"/>
-    <sheet name="4_CR" sheetId="4" r:id="rId4"/>
+    <sheet name="0_Run Process" sheetId="5" r:id="rId1"/>
+    <sheet name="CheckData" sheetId="6" r:id="rId2"/>
+    <sheet name="1_ปรับปรุงสูตร vs PY ที่ตัวเก่า" sheetId="1" r:id="rId3"/>
+    <sheet name="2_PJ202510" sheetId="2" r:id="rId4"/>
+    <sheet name="3_CR2059" sheetId="3" r:id="rId5"/>
+    <sheet name="4_CR" sheetId="4" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CheckData!$H$22:$M$44</definedName>
+    <definedName name="Sheet0_Satisfaction">'0_Run Process'!$A$85</definedName>
+    <definedName name="Sheet0_Vendor_Evaluation">'0_Run Process'!$A$1</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
+  <pivotCaches>
+    <pivotCache cacheId="75" r:id="rId7"/>
+    <pivotCache cacheId="91" r:id="rId8"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,15 +44,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="201">
   <si>
     <t>Objective</t>
   </si>
@@ -419,12 +428,297 @@
   <si>
     <t>จาก User คนไหน</t>
   </si>
+  <si>
+    <t>Vendor Evaluation</t>
+  </si>
+  <si>
+    <t>SSIS Process</t>
+  </si>
+  <si>
+    <t>01_VendorEvaluation.dtsx</t>
+  </si>
+  <si>
+    <t>BAT file &amp; Python</t>
+  </si>
+  <si>
+    <r>
+      <t>E:\Project\PROCUREMENT\BATCH\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>01_GET_DATA_FROM_SHARPOINT_VendorEvaluation.bat</t>
+    </r>
+  </si>
+  <si>
+    <t>E:\Project\PROCUREMENT\VENDOR_EVALUATION\PYTHON</t>
+  </si>
+  <si>
+    <t>_CONFIG.py</t>
+  </si>
+  <si>
+    <t>CLASS_EXPORT_SP_LIST.py</t>
+  </si>
+  <si>
+    <t>MAIN_VendorEvaluation.py</t>
+  </si>
+  <si>
+    <t>DIM.py</t>
+  </si>
+  <si>
+    <t>Working process</t>
+  </si>
+  <si>
+    <t>If it have problem on step1:</t>
+  </si>
+  <si>
+    <t>1. Go to SSIS and can run each steps.</t>
+  </si>
+  <si>
+    <t>2. Check data into SQL Database</t>
+  </si>
+  <si>
+    <t>1. Add Question Master in this year</t>
+  </si>
+  <si>
+    <t>2. Checking data in Sharepoint List that to prepare reload data</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Run job SSIS: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>01_VendorEvaluation.dtsx</t>
+    </r>
+  </si>
+  <si>
+    <t>03. Satisfaction.dtsx</t>
+  </si>
+  <si>
+    <r>
+      <t>E:\Project\PROCUREMENT\BATCH\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>03. Satisfaction.dtsx</t>
+    </r>
+  </si>
+  <si>
+    <t>MAIN_Satisfaction.py</t>
+  </si>
+  <si>
+    <t>Satisfaction</t>
+  </si>
+  <si>
+    <t>เชคข้อมูลรายคน</t>
+  </si>
+  <si>
+    <t>Question_Number</t>
+  </si>
+  <si>
+    <t>Pur_Grp</t>
+  </si>
+  <si>
+    <t>RoundYear</t>
+  </si>
+  <si>
+    <t>Cell_Value</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>STORE</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>PURCHASING</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>PACKAGING</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>ข้อมูลทั้งหมด</t>
+  </si>
+  <si>
+    <t>ข้อมูลที่ไม่ว่าง</t>
+  </si>
+  <si>
+    <t>ข้อมูลจาก MS Form</t>
+  </si>
+  <si>
+    <t>จำนวนข้อ</t>
+  </si>
+  <si>
+    <t>แถว</t>
+  </si>
+  <si>
+    <t>ข้อ</t>
+  </si>
+  <si>
+    <t>ต้องเท่ากัน</t>
+  </si>
+  <si>
+    <t>VW_FORM_06_SCORE_V2</t>
+  </si>
+  <si>
+    <t>VW_FACT_MS_FORM_GROUPING_V2</t>
+  </si>
+  <si>
+    <t>Q01</t>
+  </si>
+  <si>
+    <t>Q02</t>
+  </si>
+  <si>
+    <t>Q03</t>
+  </si>
+  <si>
+    <t>Q04</t>
+  </si>
+  <si>
+    <t>Q05</t>
+  </si>
+  <si>
+    <t>Q06</t>
+  </si>
+  <si>
+    <t>Q07</t>
+  </si>
+  <si>
+    <t>Q08</t>
+  </si>
+  <si>
+    <t>Q09</t>
+  </si>
+  <si>
+    <t>Q10</t>
+  </si>
+  <si>
+    <t>Q11</t>
+  </si>
+  <si>
+    <t>Q12</t>
+  </si>
+  <si>
+    <t>Q13</t>
+  </si>
+  <si>
+    <t>Q14</t>
+  </si>
+  <si>
+    <t>Q15</t>
+  </si>
+  <si>
+    <t>Q16</t>
+  </si>
+  <si>
+    <t>Q17</t>
+  </si>
+  <si>
+    <t>Q18</t>
+  </si>
+  <si>
+    <t>Q19</t>
+  </si>
+  <si>
+    <t>Q20</t>
+  </si>
+  <si>
+    <t>Q21</t>
+  </si>
+  <si>
+    <t>Weight_Source</t>
+  </si>
+  <si>
+    <t>VW_FACT_MS_FORM_REPORT_V2 (Trans)</t>
+  </si>
+  <si>
+    <t>VW_FACT_MS_FORM_REPORT_V2 (Group)</t>
+  </si>
+  <si>
+    <t>Question Total</t>
+  </si>
+  <si>
+    <t>Score Total</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Average of Cell_Value</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>รังสิต</t>
+  </si>
+  <si>
+    <t>ปทุมธานี</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>ALL สำหรับ Packaging เท่านั้น</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>Average of Weight_Source</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,8 +756,28 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,6 +787,54 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -501,10 +863,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -532,10 +895,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -552,6 +935,1873 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>27780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>29308</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>134937</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D2B1825-1F22-09C5-BEFF-609AD0F418CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="297350" y="1082857"/>
+          <a:ext cx="5974496" cy="458849"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>python "E:\Project\PROCUREMENT\VENDOR_EVALUATION\PYTHON\MAIN_VendorEvaluation.py"</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>python "E:\Project\PROCUREMENT\VENDOR_EVALUATION\PYTHON\DIM.py"</a:t>
+          </a:r>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>43962</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>63499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>103909</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>57727</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09EB6396-6320-25DD-B6EA-5344BF6B05B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="667417" y="1968499"/>
+          <a:ext cx="8407310" cy="10385137"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>import os</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>import CLASS_EXPORT_SP_LIST</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp = CLASS_EXPORT_SP_LIST.SharePointList()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df = sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_IT")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_IT", sharepoint_list="MS_FORM2_IT")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df = sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_LOGISTIC")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_LOGISTIC", sharepoint_list="MS_FORM2_LOGISTIC")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>#df = sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM_LOGISTIC_RENTAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>#sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_RENTAL", sharepoint_list="MS_FORM_LOGISTIC_RENTAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_WASTE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name = "STG_MS_FORM_WASTE", sharepoint_list = "MS_FORM2_WASTE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_MFG")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_MFG", sharepoint_list="MS_FORM2_MFG")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t># df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM_UNIFORM")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t># sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_UNIFORM", sharepoint_list="MS_FORM_UNIFORM")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_COM")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_COM", sharepoint_list="MS_FORM2_COM")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_OUTSOURCE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_OUTSOURCE", sharepoint_list="MS_FORM2_OUTSOURCE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_RM&amp;PKG")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_RM", sharepoint_list="MS_FORM2_RM&amp;PKG")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t># Satisfaction</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df=sp.get_dataframe_from_form_name(site_name="Satisfaction", sharepoint_list="MS_FORM_INTERNAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_INTERNAL", sharepoint_list="MS_FORM_INTERNAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df=sp.get_dataframe_from_form_name(site_name="Satisfaction", sharepoint_list="MS_FORM_EXTERNAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_EXTERNAL", sharepoint_list="MS_FORM_EXTERNAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t># Vendor Response Target</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="VENDOR_RESPONSE_TARGET")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name="STG_VENDOR_RESPONSE_TARGET", sharepoint_list="VENDOR_RESPONSE_TARGET")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t># Add for Project Vendor Evaluation V2.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df = sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_AGILE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>#sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_AGILE", sharepoint_list="MS_FORM2_AGILE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df = sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_PROPERTY")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_PROPERTY", sharepoint_list="MS_FORM2_PROPERTY")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_ENERGY_CHEMICAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name = "STG_MS_FORM_ENERGY_CHEMICAL", sharepoint_list = "MS_FORM2_ENERGY_CHEMICAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>23811</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>27780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>646042</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>134937</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38CCA8C1-E75A-4E60-9603-F1C37FFBEFBD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="294376" y="5151954"/>
+          <a:ext cx="5884449" cy="460548"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>python "E:\Project\PROCUREMENT\VENDOR_EVALUATION\PYTHON\MAIN_Satisfaction.py"</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>python "E:\Project\PROCUREMENT\VENDOR_EVALUATION\PYTHON\DIM.py"</a:t>
+          </a:r>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>27608</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>47725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>18143</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>145143</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6643D41-224C-21D2-2342-EBDD9B3DDE22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="571894" y="6579154"/>
+          <a:ext cx="5977678" cy="9894560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>import os</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>import CLASS_EXPORT_SP_LIST</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp = CLASS_EXPORT_SP_LIST.SharePointList()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df = sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_IT")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_IT", sharepoint_list="MS_FORM2_IT")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df = sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_LOGISTIC")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_LOGISTIC", sharepoint_list="MS_FORM2_LOGISTIC")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>#df = sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM_LOGISTIC_RENTAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>#sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_RENTAL", sharepoint_list="MS_FORM_LOGISTIC_RENTAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_WASTE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name = "STG_MS_FORM_WASTE", sharepoint_list = "MS_FORM2_WASTE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_MFG")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_MFG", sharepoint_list="MS_FORM2_MFG")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t># df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM_UNIFORM")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t># sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_UNIFORM", sharepoint_list="MS_FORM_UNIFORM")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_COM")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_COM", sharepoint_list="MS_FORM2_COM")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_OUTSOURCE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_OUTSOURCE", sharepoint_list="MS_FORM2_OUTSOURCE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_RM&amp;PKG")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_RM", sharepoint_list="MS_FORM2_RM&amp;PKG")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t># Satisfaction</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df=sp.get_dataframe_from_form_name(site_name="Satisfaction", sharepoint_list="MS_FORM_INTERNAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_INTERNAL", sharepoint_list="MS_FORM_INTERNAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>df=sp.get_dataframe_from_form_name(site_name="Satisfaction", sharepoint_list="MS_FORM_EXTERNAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_EXTERNAL", sharepoint_list="MS_FORM_EXTERNAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t># Vendor Response Target</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="VENDOR_RESPONSE_TARGET")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_VENDOR_RESPONSE_TARGET", sharepoint_list="VENDOR_RESPONSE_TARGET")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t># Add for Project Vendor Evaluation V2.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df = sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_AGILE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_AGILE", sharepoint_list="MS_FORM2_AGILE")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df = sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_PROPERTY")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name="STG_MS_FORM_PROPERTY", sharepoint_list="MS_FORM2_PROPERTY")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## df=sp.get_dataframe_from_form_name(site_name="ProcurementMicrosoftform", sharepoint_list="MS_FORM2_ENERGY_CHEMICAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>## sp.insert_form_dataframe_to_db(df, table_name = "STG_MS_FORM_ENERGY_CHEMICAL", sharepoint_list = "MS_FORM2_ENERGY_CHEMICAL")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>29818</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38455</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>145783</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>843</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD2C0C9A-79E4-7005-5822-5D516860EE9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13060018" y="400405"/>
+          <a:ext cx="4716540" cy="1591163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SELECT COUNT(*)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>--</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ข้อมูลทั้งหมด</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FROM [dbo].[VW_FORM_06_SCORE_V2]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>WHERE LEFT(Vendor_Name,10) = '9000103994' AND [FormYear] = 2025</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SELECT COUNT(*)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>--</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ข้อมูลที่ไม่ว่าง</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FROM [dbo].[VW_FORM_06_SCORE_V2]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>WHERE LEFT(Vendor_Name,10) = '9000103994' AND [FormYear] = 2025 AND Response_Value IS NOT NULL</a:t>
+          </a:r>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>40250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>64913</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>146690</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>43910</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{530401B0-580E-4647-E5C3-E8A446D9B8A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13128721" y="2575031"/>
+          <a:ext cx="4734469" cy="696173"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SELECT count(*)  -- </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ข้อมูลที่ไม่ว่าง</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FROM [dbo].[VW_FACT_MS_FORM_GROUPING_V2]</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>WHERE LEFT(Vendor_Name,10) = '9000103994' AND [FormYear] = 2025</a:t>
+          </a:r>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>78362</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>70130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>549729</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>18142</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C3FCB13-8FBF-4BCC-5A4A-619A33C1E0A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10945933" y="4061559"/>
+          <a:ext cx="7755725" cy="3032297"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SELECT Question_Number, Pur_Grp, RoundYear, Plant, Weight_Source, Cell_Value</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FROM VW_FACT_MS_FORM_REPORT_V2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>WHERE LEFT(Vendor_Name,10) = '9000103994' AND [FormYear] = 2025 AND LEFT(QueryPart,2) = '10' -- AND Pur_Grp = 'PACKAGING'</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ORDER BY 1,2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SELECT Question_Number, Pur_Grp, RoundYear, Plant, Cell_Value, Weight_Source</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FROM VW_FACT_MS_FORM_REPORT_V2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>WHERE LEFT(Vendor_Name,10) = '9000103994' AND [FormYear] = 2025 AND LEFT(QueryPart,2) = '20' -- AND Pur_Grp = 'PACKAGING'</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ORDER BY 1,2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SELECT Distinct REPLACE(Question_Number,'S','Q') AS Question_Number, Pur_Grp</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FROM VW_FACT_MS_FORM_REPORT_V2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>WHERE LEFT(Vendor_Name,10) = '9000103994' AND [FormYear] = 2025 AND LEFT(QueryPart,2) = '20' -- AND Pur_Grp = 'PACKAGING'</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ORDER BY 1</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>66816</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>66955</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>538183</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>103909</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E4598C3-93DB-A585-FB23-10CE30C79163}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12466634" y="9776682"/>
+          <a:ext cx="7710367" cy="2981045"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SELECT Question_Number, Pur_Grp, RoundYear, Plant, Weight_Source, Cell_Value</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FROM VW_FACT_MS_FORM_REPORT_V2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>WHERE LEFT(Vendor_Name,10) = '9000103994' AND [FormYear] = 2025 AND LEFT(QueryPart,2) = '11' -- AND Pur_Grp = 'PACKAGING'</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ORDER BY 1,2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SELECT Question_Number, Pur_Grp, RoundYear, Plant, Cell_Value, Weight_Source</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FROM VW_FACT_MS_FORM_REPORT_V2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>WHERE LEFT(Vendor_Name,10) = '9000103994' AND [FormYear] = 2025 AND LEFT(QueryPart,2) = '21' -- AND Pur_Grp = 'PACKAGING'</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ORDER BY 1,2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SELECT Distinct REPLACE(Question_Number,'S','Q') AS Question_Number, Pur_Grp</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FROM VW_FACT_MS_FORM_REPORT_V2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>WHERE LEFT(Vendor_Name,10) = '9000103994' AND [FormYear] = 2025 AND LEFT(QueryPart,2) = '20' -- AND Pur_Grp = 'PACKAGING'</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ORDER BY 1</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -604,6 +2854,481 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Sutripat Ngamjittrong" refreshedDate="46038.63841388889" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="5" xr:uid="{28BC64C3-21F0-4DE7-A222-1ED939A11B9D}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="H51:M56" sheet="CheckData"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="Question_Number" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Pur_Grp" numFmtId="0">
+      <sharedItems count="2">
+        <s v="PACKAGING"/>
+        <s v="PURCHASING"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="RoundYear" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="2"/>
+    </cacheField>
+    <cacheField name="Plant" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Cell_Value" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5" maxValue="27.5"/>
+    </cacheField>
+    <cacheField name="Weight_Source" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5" maxValue="27.5"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Sutripat Ngamjittrong" refreshedDate="46038.641298032409" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="22" xr:uid="{527B66EB-2DF2-4A3B-89C2-574FA36FEDE0}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="H22:M44" sheet="CheckData"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="Question_Number" numFmtId="0">
+      <sharedItems count="9">
+        <s v="S10"/>
+        <s v="S11"/>
+        <s v="S14"/>
+        <s v="S15"/>
+        <s v="S16"/>
+        <s v="S17"/>
+        <s v="S18"/>
+        <s v="S19"/>
+        <s v="S21"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Pur_Grp" numFmtId="0">
+      <sharedItems count="2">
+        <s v="PURCHASING"/>
+        <s v="PACKAGING"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="RoundYear" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="2" count="2">
+        <n v="1"/>
+        <n v="2"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Plant" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Cell_Value" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.9375" maxValue="10"/>
+    </cacheField>
+    <cacheField name="Weight_Source" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1.25" maxValue="10"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="5">
+  <r>
+    <s v="Score Total"/>
+    <x v="0"/>
+    <n v="1"/>
+    <s v="ALL สำหรับ Packaging เท่านั้น"/>
+    <n v="5"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <s v="Score Total"/>
+    <x v="0"/>
+    <n v="2"/>
+    <s v="ALL"/>
+    <n v="5.625"/>
+    <n v="7.5"/>
+  </r>
+  <r>
+    <s v="Score Total"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="ปทุมธานี"/>
+    <n v="25"/>
+    <n v="27.5"/>
+  </r>
+  <r>
+    <s v="Score Total"/>
+    <x v="1"/>
+    <n v="1"/>
+    <s v="รังสิต"/>
+    <n v="27.5"/>
+    <n v="27.5"/>
+  </r>
+  <r>
+    <s v="Score Total"/>
+    <x v="1"/>
+    <n v="2"/>
+    <s v="รังสิต"/>
+    <n v="25"/>
+    <n v="27.5"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="22">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="รังสิต"/>
+    <n v="10"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="ปทุมธานี"/>
+    <n v="10"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="รังสิต"/>
+    <n v="10"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="ปทุมธานี"/>
+    <n v="7.5"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="รังสิต"/>
+    <n v="7.5"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="รังสิต"/>
+    <n v="10"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="รังสิต"/>
+    <n v="1.25"/>
+    <n v="1.25"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="ปทุมธานี"/>
+    <n v="1.25"/>
+    <n v="1.25"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="รังสิต"/>
+    <n v="1.25"/>
+    <n v="1.25"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="ALL"/>
+    <n v="0.9375"/>
+    <n v="1.25"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="ALL สำหรับ Packaging เท่านั้น"/>
+    <n v="1.25"/>
+    <n v="1.25"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="รังสิต"/>
+    <n v="1.25"/>
+    <n v="1.25"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="ปทุมธานี"/>
+    <n v="1.25"/>
+    <n v="1.25"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="รังสิต"/>
+    <n v="1.25"/>
+    <n v="1.25"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="ALL สำหรับ Packaging เท่านั้น"/>
+    <n v="1.25"/>
+    <n v="1.25"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="ALL"/>
+    <n v="0.9375"/>
+    <n v="1.25"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="ALL"/>
+    <n v="1.875"/>
+    <n v="2.5"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="ALL สำหรับ Packaging เท่านั้น"/>
+    <n v="2.5"/>
+    <n v="2.5"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="ALL"/>
+    <n v="1.875"/>
+    <n v="2.5"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="รังสิต"/>
+    <n v="5"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="ปทุมธานี"/>
+    <n v="5"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="รังสิต"/>
+    <n v="5"/>
+    <n v="5"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C008B5D-E294-432C-A18D-D460E0DC566C}" name="PivotTable10" cacheId="75" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="AH51:AJ53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Average of Cell_Value" fld="4" subtotal="average" baseField="1" baseItem="0"/>
+    <dataField name="Average of Weight_Source" fld="5" subtotal="average" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC5D804D-C3A6-444E-A97A-F72693D475CD}" name="PivotTable9" cacheId="91" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="AG24:AJ33" firstHeaderRow="0" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending" defaultSubtotal="0">
+      <items count="2">
+        <item x="1"/>
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+      <items count="2">
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="5"/>
+      <x/>
+    </i>
+    <i>
+      <x v="6"/>
+      <x/>
+    </i>
+    <i>
+      <x v="7"/>
+      <x/>
+    </i>
+    <i>
+      <x v="8"/>
+      <x v="1"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Average of Cell_Value" fld="4" subtotal="average" baseField="1" baseItem="3"/>
+    <dataField name="Average of Weight_Source" fld="5" subtotal="average" baseField="1" baseItem="3"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -922,8 +3647,2358 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13A6CC10-27C7-4C7F-ABC2-5CF777CF7F18}">
+  <dimension ref="A1:T160"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="29" width="3.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:20" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C13" s="14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="17" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="18" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="22" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="23" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="24" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="25" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="26" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="27" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="28" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="29" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="30" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="31" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="32" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="33" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="35" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="36" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="37" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="38" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="39" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="40" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="41" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="42" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="43" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="44" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="45" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="46" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="47" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="48" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="49" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="50" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="51" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="52" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="53" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="54" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="55" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="56" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="57" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="58" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="59" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="60" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="61" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="62" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="63" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="64" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="70" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="13"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+    </row>
+    <row r="77" spans="1:4" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C80" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="D81" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="D82" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A85" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="12"/>
+      <c r="I85" s="12"/>
+      <c r="J85" s="12"/>
+      <c r="K85" s="12"/>
+      <c r="L85" s="12"/>
+      <c r="M85" s="12"/>
+      <c r="N85" s="12"/>
+      <c r="O85" s="12"/>
+      <c r="P85" s="12"/>
+      <c r="Q85" s="12"/>
+      <c r="R85" s="12"/>
+      <c r="S85" s="12"/>
+      <c r="T85" s="12"/>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A87" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B87" s="13"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13"/>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A89" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B89" s="13"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="93" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:20" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C95" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C96" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="99" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="100" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="101" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="103" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="106" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="3:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="113" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="114" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="115" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="116" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="117" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="118" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="119" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="120" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="121" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="122" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="123" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="124" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="125" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="126" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="127" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="128" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="129" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="130" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="131" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="132" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="133" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="134" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="135" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="136" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="137" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="138" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="139" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="140" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="141" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="142" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="143" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="144" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="145" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="146" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="147" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="148" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="149" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="150" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="151" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="152" spans="1:20" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="153" spans="1:20" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A154" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B154" s="13"/>
+      <c r="C154" s="13"/>
+      <c r="D154" s="13"/>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A155" s="15"/>
+      <c r="B155" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C155" s="15"/>
+      <c r="D155" s="15"/>
+      <c r="E155" s="15"/>
+      <c r="F155" s="15"/>
+      <c r="G155" s="15"/>
+      <c r="H155" s="15"/>
+      <c r="I155" s="15"/>
+      <c r="J155" s="15"/>
+      <c r="K155" s="15"/>
+      <c r="L155" s="15"/>
+      <c r="M155" s="15"/>
+      <c r="N155" s="15"/>
+      <c r="O155" s="15"/>
+      <c r="P155" s="15"/>
+      <c r="Q155" s="15"/>
+      <c r="R155" s="15"/>
+      <c r="S155" s="15"/>
+      <c r="T155" s="15"/>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A156" s="15"/>
+      <c r="B156" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C156" s="15"/>
+      <c r="D156" s="15"/>
+      <c r="E156" s="15"/>
+      <c r="F156" s="15"/>
+      <c r="G156" s="15"/>
+      <c r="H156" s="15"/>
+      <c r="I156" s="15"/>
+      <c r="J156" s="15"/>
+      <c r="K156" s="15"/>
+      <c r="L156" s="15"/>
+      <c r="M156" s="15"/>
+      <c r="N156" s="15"/>
+      <c r="O156" s="15"/>
+      <c r="P156" s="15"/>
+      <c r="Q156" s="15"/>
+      <c r="R156" s="15"/>
+      <c r="S156" s="15"/>
+      <c r="T156" s="15"/>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B157" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C158" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="D159" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="D160" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A85:T85"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C65F5FD-F282-4644-92C9-1C5B0B925E70}">
+  <dimension ref="A1:AK72"/>
+  <sheetFormatPr defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.08203125" customWidth="1"/>
+    <col min="2" max="2" width="11.9140625" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="19" max="31" width="8.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="32" width="8.6640625" collapsed="1"/>
+    <col min="33" max="33" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="26.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+    </row>
+    <row r="3" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="18">
+        <v>231</v>
+      </c>
+      <c r="C3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="18">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="18">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" s="18">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8">
+        <f>B6*B7</f>
+        <v>231</v>
+      </c>
+      <c r="C8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="21" t="b">
+        <f>B8=B3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:3" collapsed="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+    </row>
+    <row r="15" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="18">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:36" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="21" t="b">
+        <f>B15=B4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:36" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:36" collapsed="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" t="s">
+        <v>194</v>
+      </c>
+      <c r="E22" t="s">
+        <v>187</v>
+      </c>
+      <c r="F22" t="s">
+        <v>143</v>
+      </c>
+      <c r="H22" t="s">
+        <v>140</v>
+      </c>
+      <c r="I22" t="s">
+        <v>141</v>
+      </c>
+      <c r="J22" t="s">
+        <v>142</v>
+      </c>
+      <c r="K22" t="s">
+        <v>194</v>
+      </c>
+      <c r="L22" t="s">
+        <v>143</v>
+      </c>
+      <c r="M22" t="s">
+        <v>187</v>
+      </c>
+      <c r="O22" t="s">
+        <v>140</v>
+      </c>
+      <c r="P22" t="s">
+        <v>141</v>
+      </c>
+      <c r="AG22" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>195</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="H23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I23" t="s">
+        <v>147</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
+        <v>195</v>
+      </c>
+      <c r="L23">
+        <v>10</v>
+      </c>
+      <c r="M23">
+        <v>10</v>
+      </c>
+      <c r="O23" t="s">
+        <v>166</v>
+      </c>
+      <c r="P23" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q23" s="22"/>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>175</v>
+      </c>
+      <c r="B24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="H24" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" t="s">
+        <v>147</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24" t="s">
+        <v>196</v>
+      </c>
+      <c r="L24">
+        <v>10</v>
+      </c>
+      <c r="M24">
+        <v>10</v>
+      </c>
+      <c r="O24" t="s">
+        <v>167</v>
+      </c>
+      <c r="P24" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q24" s="22"/>
+      <c r="AG24" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH24" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>193</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>175</v>
+      </c>
+      <c r="B25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>195</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="H25" t="s">
+        <v>146</v>
+      </c>
+      <c r="I25" t="s">
+        <v>147</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25" t="s">
+        <v>195</v>
+      </c>
+      <c r="L25">
+        <v>10</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
+      </c>
+      <c r="O25" t="s">
+        <v>168</v>
+      </c>
+      <c r="P25" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q25" s="22"/>
+      <c r="AG25" t="s">
+        <v>146</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>147</v>
+      </c>
+      <c r="AI25" s="25">
+        <v>10</v>
+      </c>
+      <c r="AJ25" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>196</v>
+      </c>
+      <c r="E26">
+        <v>10</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="H26" t="s">
+        <v>148</v>
+      </c>
+      <c r="I26" t="s">
+        <v>147</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26" t="s">
+        <v>196</v>
+      </c>
+      <c r="L26">
+        <v>7.5</v>
+      </c>
+      <c r="M26">
+        <v>10</v>
+      </c>
+      <c r="O26" t="s">
+        <v>169</v>
+      </c>
+      <c r="P26" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q26" s="17"/>
+      <c r="AG26" t="s">
+        <v>148</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>147</v>
+      </c>
+      <c r="AI26" s="25">
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="AJ26" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="H27" t="s">
+        <v>148</v>
+      </c>
+      <c r="I27" t="s">
+        <v>147</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>195</v>
+      </c>
+      <c r="L27">
+        <v>7.5</v>
+      </c>
+      <c r="M27">
+        <v>10</v>
+      </c>
+      <c r="O27" t="s">
+        <v>170</v>
+      </c>
+      <c r="P27" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q27" s="17"/>
+      <c r="AG27" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>147</v>
+      </c>
+      <c r="AI27" s="25">
+        <v>1.25</v>
+      </c>
+      <c r="AJ27" s="25">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>176</v>
+      </c>
+      <c r="B28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>195</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="H28" t="s">
+        <v>148</v>
+      </c>
+      <c r="I28" t="s">
+        <v>147</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" t="s">
+        <v>195</v>
+      </c>
+      <c r="L28">
+        <v>10</v>
+      </c>
+      <c r="M28">
+        <v>10</v>
+      </c>
+      <c r="O28" t="s">
+        <v>171</v>
+      </c>
+      <c r="P28" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q28" s="17"/>
+      <c r="AG28" t="s">
+        <v>150</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>151</v>
+      </c>
+      <c r="AI28" s="25">
+        <v>1.09375</v>
+      </c>
+      <c r="AJ28" s="25">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>179</v>
+      </c>
+      <c r="B29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29">
+        <v>1.25</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="H29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I29" t="s">
+        <v>147</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29" t="s">
+        <v>195</v>
+      </c>
+      <c r="L29">
+        <v>1.25</v>
+      </c>
+      <c r="M29">
+        <v>1.25</v>
+      </c>
+      <c r="O29" t="s">
+        <v>172</v>
+      </c>
+      <c r="P29" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q29" s="17"/>
+      <c r="AG29" t="s">
+        <v>152</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>147</v>
+      </c>
+      <c r="AI29" s="25">
+        <v>1.25</v>
+      </c>
+      <c r="AJ29" s="25">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>179</v>
+      </c>
+      <c r="B30" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30">
+        <v>1.25</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="H30" t="s">
+        <v>149</v>
+      </c>
+      <c r="I30" t="s">
+        <v>147</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30" t="s">
+        <v>196</v>
+      </c>
+      <c r="L30">
+        <v>1.25</v>
+      </c>
+      <c r="M30">
+        <v>1.25</v>
+      </c>
+      <c r="O30" t="s">
+        <v>173</v>
+      </c>
+      <c r="P30" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q30" s="17"/>
+      <c r="AG30" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>151</v>
+      </c>
+      <c r="AI30" s="25">
+        <v>1.09375</v>
+      </c>
+      <c r="AJ30" s="25">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>195</v>
+      </c>
+      <c r="E31">
+        <v>1.25</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="H31" t="s">
+        <v>149</v>
+      </c>
+      <c r="I31" t="s">
+        <v>147</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31" t="s">
+        <v>195</v>
+      </c>
+      <c r="L31">
+        <v>1.25</v>
+      </c>
+      <c r="M31">
+        <v>1.25</v>
+      </c>
+      <c r="O31" t="s">
+        <v>174</v>
+      </c>
+      <c r="P31" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q31" s="17"/>
+      <c r="AG31" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>151</v>
+      </c>
+      <c r="AI31" s="25">
+        <v>2.1875</v>
+      </c>
+      <c r="AJ31" s="25">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>180</v>
+      </c>
+      <c r="B32" t="s">
+        <v>151</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>197</v>
+      </c>
+      <c r="E32">
+        <v>1.25</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="H32" t="s">
+        <v>150</v>
+      </c>
+      <c r="I32" t="s">
+        <v>151</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>197</v>
+      </c>
+      <c r="L32">
+        <v>0.9375</v>
+      </c>
+      <c r="M32">
+        <v>1.25</v>
+      </c>
+      <c r="O32" t="s">
+        <v>175</v>
+      </c>
+      <c r="P32" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q32" s="9"/>
+      <c r="AG32" t="s">
+        <v>155</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>151</v>
+      </c>
+      <c r="AI32" s="25">
+        <v>1.875</v>
+      </c>
+      <c r="AJ32" s="25">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33" t="s">
+        <v>151</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33">
+        <v>1.25</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="H33" t="s">
+        <v>150</v>
+      </c>
+      <c r="I33" t="s">
+        <v>151</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" t="s">
+        <v>198</v>
+      </c>
+      <c r="L33">
+        <v>1.25</v>
+      </c>
+      <c r="M33">
+        <v>1.25</v>
+      </c>
+      <c r="O33" t="s">
+        <v>176</v>
+      </c>
+      <c r="P33" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q33" s="9"/>
+      <c r="AG33" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>147</v>
+      </c>
+      <c r="AI33" s="25">
+        <v>5</v>
+      </c>
+      <c r="AJ33" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>181</v>
+      </c>
+      <c r="B34" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34">
+        <v>1.25</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="H34" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34" t="s">
+        <v>147</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" t="s">
+        <v>195</v>
+      </c>
+      <c r="L34">
+        <v>1.25</v>
+      </c>
+      <c r="M34">
+        <v>1.25</v>
+      </c>
+      <c r="O34" t="s">
+        <v>177</v>
+      </c>
+      <c r="P34" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q34" s="22"/>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>196</v>
+      </c>
+      <c r="E35">
+        <v>1.25</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="H35" t="s">
+        <v>152</v>
+      </c>
+      <c r="I35" t="s">
+        <v>147</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35" t="s">
+        <v>196</v>
+      </c>
+      <c r="L35">
+        <v>1.25</v>
+      </c>
+      <c r="M35">
+        <v>1.25</v>
+      </c>
+      <c r="O35" t="s">
+        <v>178</v>
+      </c>
+      <c r="P35" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q35" s="22"/>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36">
+        <v>1.25</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="H36" t="s">
+        <v>152</v>
+      </c>
+      <c r="I36" t="s">
+        <v>147</v>
+      </c>
+      <c r="J36">
+        <v>2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>195</v>
+      </c>
+      <c r="L36">
+        <v>1.25</v>
+      </c>
+      <c r="M36">
+        <v>1.25</v>
+      </c>
+      <c r="O36" t="s">
+        <v>179</v>
+      </c>
+      <c r="P36" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q36" s="9"/>
+      <c r="AI36" s="26">
+        <f>SUMIF(AI25:AI33,"&lt;&gt;0")</f>
+        <v>32.083333333333336</v>
+      </c>
+      <c r="AJ36" s="27">
+        <f>SUMIF(AI25:AI33,"&lt;&gt;0",AJ25:AJ33)</f>
+        <v>35</v>
+      </c>
+      <c r="AK36" s="14">
+        <f>AI36/AJ36*100</f>
+        <v>91.666666666666671</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>182</v>
+      </c>
+      <c r="B37" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>198</v>
+      </c>
+      <c r="E37">
+        <v>1.25</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="H37" t="s">
+        <v>153</v>
+      </c>
+      <c r="I37" t="s">
+        <v>151</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37" t="s">
+        <v>198</v>
+      </c>
+      <c r="L37">
+        <v>1.25</v>
+      </c>
+      <c r="M37">
+        <v>1.25</v>
+      </c>
+      <c r="O37" t="s">
+        <v>180</v>
+      </c>
+      <c r="P37" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q37" s="21"/>
+    </row>
+    <row r="38" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>182</v>
+      </c>
+      <c r="B38" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38" t="s">
+        <v>197</v>
+      </c>
+      <c r="E38">
+        <v>1.25</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="H38" t="s">
+        <v>153</v>
+      </c>
+      <c r="I38" t="s">
+        <v>151</v>
+      </c>
+      <c r="J38">
+        <v>2</v>
+      </c>
+      <c r="K38" t="s">
+        <v>197</v>
+      </c>
+      <c r="L38">
+        <v>0.9375</v>
+      </c>
+      <c r="M38">
+        <v>1.25</v>
+      </c>
+      <c r="O38" t="s">
+        <v>181</v>
+      </c>
+      <c r="P38" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q38" s="9"/>
+    </row>
+    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>183</v>
+      </c>
+      <c r="B39" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E39">
+        <v>2.5</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="H39" t="s">
+        <v>154</v>
+      </c>
+      <c r="I39" t="s">
+        <v>151</v>
+      </c>
+      <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="K39" t="s">
+        <v>197</v>
+      </c>
+      <c r="L39">
+        <v>1.875</v>
+      </c>
+      <c r="M39">
+        <v>2.5</v>
+      </c>
+      <c r="O39" t="s">
+        <v>182</v>
+      </c>
+      <c r="P39" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q39" s="21"/>
+      <c r="AH39" t="s">
+        <v>151</v>
+      </c>
+      <c r="AI39">
+        <f>SUMIF($AH$25:$AH$33,AH39,$AI$25:$AI$33)</f>
+        <v>6.25</v>
+      </c>
+      <c r="AJ39">
+        <f>SUMIFS($AJ$25:$AJ$33,$AH$25:$AH$33, AH39, $AI$25:$AI$33, "&lt;&gt;0")</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>183</v>
+      </c>
+      <c r="B40" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>198</v>
+      </c>
+      <c r="E40">
+        <v>2.5</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="H40" t="s">
+        <v>154</v>
+      </c>
+      <c r="I40" t="s">
+        <v>151</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40" t="s">
+        <v>198</v>
+      </c>
+      <c r="L40">
+        <v>2.5</v>
+      </c>
+      <c r="M40">
+        <v>2.5</v>
+      </c>
+      <c r="O40" t="s">
+        <v>183</v>
+      </c>
+      <c r="P40" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q40" s="21"/>
+      <c r="AH40" t="s">
+        <v>147</v>
+      </c>
+      <c r="AI40">
+        <f t="shared" ref="AI40:AI42" si="0">SUMIF($AH$25:$AH$33,AH40,$AI$25:$AI$33)</f>
+        <v>25.833333333333336</v>
+      </c>
+      <c r="AJ40">
+        <f t="shared" ref="AJ40:AJ42" si="1">SUMIFS($AJ$25:$AJ$33,$AH$25:$AH$33, AH40, $AI$25:$AI$33, "&lt;&gt;0")</f>
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>197</v>
+      </c>
+      <c r="E41">
+        <v>2.5</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="H41" t="s">
+        <v>155</v>
+      </c>
+      <c r="I41" t="s">
+        <v>151</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41" t="s">
+        <v>197</v>
+      </c>
+      <c r="L41">
+        <v>1.875</v>
+      </c>
+      <c r="M41">
+        <v>2.5</v>
+      </c>
+      <c r="O41" t="s">
+        <v>184</v>
+      </c>
+      <c r="P41" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q41" s="21"/>
+      <c r="AH41" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>186</v>
+      </c>
+      <c r="B42" t="s">
+        <v>147</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>195</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="H42" t="s">
+        <v>156</v>
+      </c>
+      <c r="I42" t="s">
+        <v>147</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="s">
+        <v>195</v>
+      </c>
+      <c r="L42">
+        <v>5</v>
+      </c>
+      <c r="M42">
+        <v>5</v>
+      </c>
+      <c r="O42" t="s">
+        <v>185</v>
+      </c>
+      <c r="P42" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q42" s="20"/>
+      <c r="AH42" t="s">
+        <v>145</v>
+      </c>
+      <c r="AI42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ42">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>186</v>
+      </c>
+      <c r="B43" t="s">
+        <v>147</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>196</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="H43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I43" t="s">
+        <v>147</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43" t="s">
+        <v>196</v>
+      </c>
+      <c r="L43">
+        <v>5</v>
+      </c>
+      <c r="M43">
+        <v>5</v>
+      </c>
+      <c r="O43" t="s">
+        <v>186</v>
+      </c>
+      <c r="P43" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q43" s="9"/>
+      <c r="AI43" s="13">
+        <f>SUM(AI39:AI42)</f>
+        <v>32.083333333333336</v>
+      </c>
+      <c r="AJ43" s="27">
+        <f>SUM(AJ39:AJ42)</f>
+        <v>35</v>
+      </c>
+      <c r="AK43" s="14">
+        <f>AI43/AJ43*100</f>
+        <v>91.666666666666671</v>
+      </c>
+    </row>
+    <row r="44" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>186</v>
+      </c>
+      <c r="B44" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>195</v>
+      </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
+      <c r="H44" t="s">
+        <v>156</v>
+      </c>
+      <c r="I44" t="s">
+        <v>147</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44" t="s">
+        <v>195</v>
+      </c>
+      <c r="L44">
+        <v>5</v>
+      </c>
+      <c r="M44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A50" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+    </row>
+    <row r="51" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A51" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="L51" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="M51" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="O51" t="s">
+        <v>140</v>
+      </c>
+      <c r="P51" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH51" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>193</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A52" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" s="15">
+        <v>1</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="E52" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="F52" s="15">
+        <v>12</v>
+      </c>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="I52" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="J52" s="15">
+        <v>1</v>
+      </c>
+      <c r="K52" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="L52" s="15">
+        <v>5</v>
+      </c>
+      <c r="M52" s="15">
+        <v>5</v>
+      </c>
+      <c r="O52" t="s">
+        <v>166</v>
+      </c>
+      <c r="P52" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q52" s="22"/>
+      <c r="AH52" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="AI52" s="25">
+        <v>5.3125</v>
+      </c>
+      <c r="AJ52" s="25">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A53" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C53" s="15">
+        <v>2</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E53" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="F53" s="15">
+        <v>12</v>
+      </c>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="I53" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="J53" s="15">
+        <v>2</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="L53" s="15">
+        <v>5.625</v>
+      </c>
+      <c r="M53" s="15">
+        <v>7.5</v>
+      </c>
+      <c r="O53" t="s">
+        <v>167</v>
+      </c>
+      <c r="P53" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q53" s="22"/>
+      <c r="AH53" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="AI53" s="25">
+        <v>25.833333333333332</v>
+      </c>
+      <c r="AJ53" s="25">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A54" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C54" s="15">
+        <v>2</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="E54" s="15">
+        <v>10</v>
+      </c>
+      <c r="F54" s="15">
+        <v>19</v>
+      </c>
+      <c r="G54" s="15"/>
+      <c r="H54" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="I54" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J54" s="15">
+        <v>2</v>
+      </c>
+      <c r="K54" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="L54" s="15">
+        <v>25</v>
+      </c>
+      <c r="M54" s="15">
+        <v>27.5</v>
+      </c>
+      <c r="O54" t="s">
+        <v>168</v>
+      </c>
+      <c r="P54" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q54" s="22"/>
+    </row>
+    <row r="55" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A55" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" s="15">
+        <v>1</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="E55" s="15">
+        <v>10</v>
+      </c>
+      <c r="F55" s="15">
+        <v>20</v>
+      </c>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="I55" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J55" s="15">
+        <v>1</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="L55" s="15">
+        <v>27.5</v>
+      </c>
+      <c r="M55" s="15">
+        <v>27.5</v>
+      </c>
+      <c r="O55" t="s">
+        <v>169</v>
+      </c>
+      <c r="P55" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q55" s="17"/>
+    </row>
+    <row r="56" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A56" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" s="15">
+        <v>2</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="E56" s="15">
+        <v>10</v>
+      </c>
+      <c r="F56" s="15">
+        <v>19</v>
+      </c>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="I56" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J56" s="15">
+        <v>2</v>
+      </c>
+      <c r="K56" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="L56" s="15">
+        <v>25</v>
+      </c>
+      <c r="M56" s="15">
+        <v>27.5</v>
+      </c>
+      <c r="O56" t="s">
+        <v>170</v>
+      </c>
+      <c r="P56" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q56" s="17"/>
+      <c r="AI56" s="1">
+        <f>SUM(AI52:AI53)</f>
+        <v>31.145833333333332</v>
+      </c>
+      <c r="AJ56">
+        <f>SUM(AJ52:AJ53)</f>
+        <v>33.75</v>
+      </c>
+      <c r="AK56">
+        <f>AI56/AJ56*100</f>
+        <v>92.283950617283949</v>
+      </c>
+    </row>
+    <row r="57" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A57" s="15"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="15"/>
+      <c r="O57" t="s">
+        <v>171</v>
+      </c>
+      <c r="P57" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q57" s="17"/>
+    </row>
+    <row r="58" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="15"/>
+      <c r="O58" t="s">
+        <v>172</v>
+      </c>
+      <c r="P58" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q58" s="17"/>
+    </row>
+    <row r="59" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A59" s="15"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+      <c r="L59" s="15"/>
+      <c r="M59" s="15"/>
+      <c r="O59" t="s">
+        <v>173</v>
+      </c>
+      <c r="P59" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q59" s="17"/>
+    </row>
+    <row r="60" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="O60" t="s">
+        <v>174</v>
+      </c>
+      <c r="P60" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q60" s="17"/>
+    </row>
+    <row r="61" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A61" s="15"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="15"/>
+      <c r="O61" t="s">
+        <v>175</v>
+      </c>
+      <c r="P61" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q61" s="9"/>
+    </row>
+    <row r="62" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A62" s="15"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15"/>
+      <c r="G62" s="15"/>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="15"/>
+      <c r="O62" t="s">
+        <v>176</v>
+      </c>
+      <c r="P62" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q62" s="9"/>
+    </row>
+    <row r="63" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A63" s="15"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="15"/>
+      <c r="G63" s="15"/>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="15"/>
+      <c r="M63" s="15"/>
+      <c r="O63" t="s">
+        <v>177</v>
+      </c>
+      <c r="P63" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q63" s="22"/>
+    </row>
+    <row r="64" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A64" s="15"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="15"/>
+      <c r="M64" s="15"/>
+      <c r="O64" t="s">
+        <v>178</v>
+      </c>
+      <c r="P64" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q64" s="22"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A65" s="15"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="15"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="15"/>
+      <c r="M65" s="15"/>
+      <c r="O65" t="s">
+        <v>179</v>
+      </c>
+      <c r="P65" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q65" s="9"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O66" t="s">
+        <v>180</v>
+      </c>
+      <c r="P66" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q66" s="21"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O67" t="s">
+        <v>181</v>
+      </c>
+      <c r="P67" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q67" s="9"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O68" t="s">
+        <v>182</v>
+      </c>
+      <c r="P68" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q68" s="21"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O69" t="s">
+        <v>183</v>
+      </c>
+      <c r="P69" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q69" s="21"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O70" t="s">
+        <v>184</v>
+      </c>
+      <c r="P70" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q70" s="21"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O71" t="s">
+        <v>185</v>
+      </c>
+      <c r="P71" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q71" s="20"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O72" t="s">
+        <v>186</v>
+      </c>
+      <c r="P72" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q72" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="20" width="4.08203125" customWidth="1"/>
@@ -944,6 +6019,9 @@
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -954,9 +6032,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F471E627-EFC1-432D-A8D8-9AA7B0826CF8}">
-  <dimension ref="A1:W83"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr defaultRowHeight="14" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="26" width="4.08203125" customWidth="1"/>
@@ -1739,7 +6817,7 @@
     </row>
     <row r="71" spans="1:10" collapsed="1" x14ac:dyDescent="0.3"/>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="11" t="s">
+      <c r="A72" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1775,7 +6853,7 @@
     </row>
     <row r="79" spans="1:10" collapsed="1" x14ac:dyDescent="0.3"/>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="11" t="s">
+      <c r="A80" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1799,7 +6877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04E0BB-84CD-4788-9BF6-07133E7B251F}">
   <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -1979,7 +7057,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="11" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2014,7 +7092,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB28340-1023-4EA8-9E13-B74161134F70}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
